--- a/模板/承认书空白模板_通用.xlsx
+++ b/模板/承认书空白模板_通用.xlsx
@@ -6602,7 +6602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col width="8.625" customWidth="1" style="1" min="1" max="1"/>
@@ -6766,7 +6766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col width="8.625" customWidth="1" style="1" min="1" max="1"/>
@@ -6852,11 +6852,7 @@
     </row>
     <row r="14" ht="28.15" customHeight="1" s="294">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>线材             端子胶壳                   套管</t>
-        </is>
-      </c>
+      <c r="B14" s="14" t="n"/>
       <c r="C14" s="6" t="n"/>
     </row>
     <row r="15" ht="28.15" customHeight="1" s="294">
@@ -10429,7 +10425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col width="8.625" customWidth="1" style="1" min="1" max="1"/>
@@ -10520,11 +10516,7 @@
     </row>
     <row r="15" ht="28.15" customHeight="1" s="294">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">线材              端子胶壳           套管    </t>
-        </is>
-      </c>
+      <c r="B15" s="14" t="n"/>
       <c r="C15" s="6" t="n"/>
     </row>
     <row r="16" ht="28.15" customHeight="1" s="294">
@@ -10795,11 +10787,7 @@
           <t>Product name:</t>
         </is>
       </c>
-      <c r="C2" s="117" t="inlineStr">
-        <is>
-          <t>导线</t>
-        </is>
-      </c>
+      <c r="C2" s="117" t="n"/>
       <c r="G2" s="118" t="inlineStr">
         <is>
           <t>Drawing No:</t>
@@ -10823,11 +10811,7 @@
           <t>Date:</t>
         </is>
       </c>
-      <c r="U2" s="117" t="inlineStr">
-        <is>
-          <t>2026.06.18</t>
-        </is>
-      </c>
+      <c r="U2" s="117" t="n"/>
       <c r="Y2" s="118" t="inlineStr">
         <is>
           <t>Confirm by:</t>
@@ -11235,15 +11219,9 @@
       <c r="A9" s="148" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="145" t="n">
-        <v>93</v>
-      </c>
-      <c r="C9" s="145" t="n">
-        <v>98</v>
-      </c>
-      <c r="D9" s="145" t="n">
-        <v>103</v>
-      </c>
+      <c r="B9" s="145" t="n"/>
+      <c r="C9" s="145" t="n"/>
+      <c r="D9" s="145" t="n"/>
       <c r="E9" s="148">
         <f>AVERAGE(I9:AN9)</f>
         <v/>
@@ -11260,102 +11238,38 @@
         <f>MIN(((D9-E9)/(3*F9)),((E9-B9)/(3*F9)))</f>
         <v/>
       </c>
-      <c r="I9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="J9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="K9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="L9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="M9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="N9" s="144" t="n">
-        <v>99</v>
-      </c>
-      <c r="O9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="P9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="Q9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="R9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="S9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="T9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="U9" s="144" t="n">
-        <v>99</v>
-      </c>
-      <c r="V9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="W9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="X9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="Y9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="Z9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="AA9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="AB9" s="144" t="n">
-        <v>99</v>
-      </c>
-      <c r="AC9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="AD9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="AE9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="AF9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="AG9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="AH9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="AI9" s="144" t="n">
-        <v>99</v>
-      </c>
-      <c r="AJ9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="AK9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="AL9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="AM9" s="144" t="n">
-        <v>98</v>
-      </c>
-      <c r="AN9" s="146" t="n">
-        <v>99</v>
-      </c>
+      <c r="I9" s="144" t="n"/>
+      <c r="J9" s="144" t="n"/>
+      <c r="K9" s="144" t="n"/>
+      <c r="L9" s="144" t="n"/>
+      <c r="M9" s="144" t="n"/>
+      <c r="N9" s="144" t="n"/>
+      <c r="O9" s="144" t="n"/>
+      <c r="P9" s="144" t="n"/>
+      <c r="Q9" s="144" t="n"/>
+      <c r="R9" s="144" t="n"/>
+      <c r="S9" s="144" t="n"/>
+      <c r="T9" s="144" t="n"/>
+      <c r="U9" s="144" t="n"/>
+      <c r="V9" s="144" t="n"/>
+      <c r="W9" s="144" t="n"/>
+      <c r="X9" s="144" t="n"/>
+      <c r="Y9" s="144" t="n"/>
+      <c r="Z9" s="144" t="n"/>
+      <c r="AA9" s="144" t="n"/>
+      <c r="AB9" s="144" t="n"/>
+      <c r="AC9" s="144" t="n"/>
+      <c r="AD9" s="144" t="n"/>
+      <c r="AE9" s="144" t="n"/>
+      <c r="AF9" s="144" t="n"/>
+      <c r="AG9" s="144" t="n"/>
+      <c r="AH9" s="144" t="n"/>
+      <c r="AI9" s="144" t="n"/>
+      <c r="AJ9" s="144" t="n"/>
+      <c r="AK9" s="144" t="n"/>
+      <c r="AL9" s="144" t="n"/>
+      <c r="AM9" s="144" t="n"/>
+      <c r="AN9" s="146" t="n"/>
       <c r="AO9" s="147" t="inlineStr">
         <is>
           <t>Z</t>
@@ -11367,15 +11281,9 @@
       <c r="A10" s="148" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="145" t="n">
-        <v>55</v>
-      </c>
-      <c r="C10" s="145" t="n">
-        <v>60</v>
-      </c>
-      <c r="D10" s="152" t="n">
-        <v>65</v>
-      </c>
+      <c r="B10" s="145" t="n"/>
+      <c r="C10" s="145" t="n"/>
+      <c r="D10" s="152" t="n"/>
       <c r="E10" s="148">
         <f>AVERAGE(I10:AN10)</f>
         <v/>
@@ -11392,102 +11300,38 @@
         <f>MIN(((D10-E10)/(3*F10)),((E10-B10)/(3*F10)))</f>
         <v/>
       </c>
-      <c r="I10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="J10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="K10" s="144" t="n">
-        <v>61</v>
-      </c>
-      <c r="L10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="M10" s="144" t="n">
-        <v>61</v>
-      </c>
-      <c r="N10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="O10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="P10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="R10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="S10" s="144" t="n">
-        <v>61</v>
-      </c>
-      <c r="T10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="U10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="V10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="W10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="X10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="Y10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z10" s="144" t="n">
-        <v>61</v>
-      </c>
-      <c r="AA10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="AD10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="AE10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="AG10" s="144" t="n">
-        <v>61</v>
-      </c>
-      <c r="AH10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM10" s="144" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN10" s="146" t="n">
-        <v>61</v>
-      </c>
+      <c r="I10" s="144" t="n"/>
+      <c r="J10" s="144" t="n"/>
+      <c r="K10" s="144" t="n"/>
+      <c r="L10" s="144" t="n"/>
+      <c r="M10" s="144" t="n"/>
+      <c r="N10" s="144" t="n"/>
+      <c r="O10" s="144" t="n"/>
+      <c r="P10" s="144" t="n"/>
+      <c r="Q10" s="144" t="n"/>
+      <c r="R10" s="144" t="n"/>
+      <c r="S10" s="144" t="n"/>
+      <c r="T10" s="144" t="n"/>
+      <c r="U10" s="144" t="n"/>
+      <c r="V10" s="144" t="n"/>
+      <c r="W10" s="144" t="n"/>
+      <c r="X10" s="144" t="n"/>
+      <c r="Y10" s="144" t="n"/>
+      <c r="Z10" s="144" t="n"/>
+      <c r="AA10" s="144" t="n"/>
+      <c r="AB10" s="144" t="n"/>
+      <c r="AC10" s="144" t="n"/>
+      <c r="AD10" s="144" t="n"/>
+      <c r="AE10" s="144" t="n"/>
+      <c r="AF10" s="144" t="n"/>
+      <c r="AG10" s="144" t="n"/>
+      <c r="AH10" s="144" t="n"/>
+      <c r="AI10" s="144" t="n"/>
+      <c r="AJ10" s="144" t="n"/>
+      <c r="AK10" s="144" t="n"/>
+      <c r="AL10" s="144" t="n"/>
+      <c r="AM10" s="144" t="n"/>
+      <c r="AN10" s="146" t="n"/>
       <c r="AO10" s="144" t="inlineStr">
         <is>
           <t>Z</t>
@@ -11499,15 +11343,9 @@
       <c r="A11" s="148" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="145" t="n">
-        <v>25</v>
-      </c>
-      <c r="C11" s="145" t="n">
-        <v>28</v>
-      </c>
-      <c r="D11" s="152" t="n">
-        <v>31</v>
-      </c>
+      <c r="B11" s="145" t="n"/>
+      <c r="C11" s="145" t="n"/>
+      <c r="D11" s="152" t="n"/>
       <c r="E11" s="148">
         <f>AVERAGE(I11:AN11)</f>
         <v/>
@@ -11524,102 +11362,38 @@
         <f>MIN(((D11-E11)/(3*F11)),((E11-B11)/(3*F11)))</f>
         <v/>
       </c>
-      <c r="I11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="J11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="K11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="L11" s="153" t="n">
-        <v>29</v>
-      </c>
-      <c r="M11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="N11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="O11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="P11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="R11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="S11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="T11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="U11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="V11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="W11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="X11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z11" s="153" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="AD11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM11" s="153" t="n">
-        <v>28</v>
-      </c>
-      <c r="AN11" s="154" t="n">
-        <v>29</v>
-      </c>
+      <c r="I11" s="153" t="n"/>
+      <c r="J11" s="153" t="n"/>
+      <c r="K11" s="153" t="n"/>
+      <c r="L11" s="153" t="n"/>
+      <c r="M11" s="153" t="n"/>
+      <c r="N11" s="153" t="n"/>
+      <c r="O11" s="153" t="n"/>
+      <c r="P11" s="153" t="n"/>
+      <c r="Q11" s="153" t="n"/>
+      <c r="R11" s="153" t="n"/>
+      <c r="S11" s="153" t="n"/>
+      <c r="T11" s="153" t="n"/>
+      <c r="U11" s="153" t="n"/>
+      <c r="V11" s="153" t="n"/>
+      <c r="W11" s="153" t="n"/>
+      <c r="X11" s="153" t="n"/>
+      <c r="Y11" s="153" t="n"/>
+      <c r="Z11" s="153" t="n"/>
+      <c r="AA11" s="153" t="n"/>
+      <c r="AB11" s="153" t="n"/>
+      <c r="AC11" s="153" t="n"/>
+      <c r="AD11" s="153" t="n"/>
+      <c r="AE11" s="153" t="n"/>
+      <c r="AF11" s="153" t="n"/>
+      <c r="AG11" s="153" t="n"/>
+      <c r="AH11" s="153" t="n"/>
+      <c r="AI11" s="153" t="n"/>
+      <c r="AJ11" s="153" t="n"/>
+      <c r="AK11" s="153" t="n"/>
+      <c r="AL11" s="153" t="n"/>
+      <c r="AM11" s="153" t="n"/>
+      <c r="AN11" s="154" t="n"/>
       <c r="AO11" s="144" t="inlineStr">
         <is>
           <t>Z</t>
@@ -11631,15 +11405,9 @@
       <c r="A12" s="148" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="145" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C12" s="145" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="152" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="B12" s="145" t="n"/>
+      <c r="C12" s="145" t="n"/>
+      <c r="D12" s="152" t="n"/>
       <c r="E12" s="148">
         <f>AVERAGE(I12:AN12)</f>
         <v/>
@@ -11656,102 +11424,38 @@
         <f>MIN(((D12-E12)/(3*F12)),((E12-B12)/(3*F12)))</f>
         <v/>
       </c>
-      <c r="I12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K12" s="153" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="M12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O12" s="153" t="n">
-        <v>2</v>
-      </c>
-      <c r="P12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U12" s="153" t="n">
-        <v>2</v>
-      </c>
-      <c r="V12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="X12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB12" s="153" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI12" s="153" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AK12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM12" s="153" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AN12" s="155" t="n">
-        <v>2</v>
-      </c>
+      <c r="I12" s="153" t="n"/>
+      <c r="J12" s="153" t="n"/>
+      <c r="K12" s="153" t="n"/>
+      <c r="L12" s="153" t="n"/>
+      <c r="M12" s="153" t="n"/>
+      <c r="N12" s="153" t="n"/>
+      <c r="O12" s="153" t="n"/>
+      <c r="P12" s="153" t="n"/>
+      <c r="Q12" s="153" t="n"/>
+      <c r="R12" s="153" t="n"/>
+      <c r="S12" s="153" t="n"/>
+      <c r="T12" s="153" t="n"/>
+      <c r="U12" s="153" t="n"/>
+      <c r="V12" s="153" t="n"/>
+      <c r="W12" s="153" t="n"/>
+      <c r="X12" s="153" t="n"/>
+      <c r="Y12" s="153" t="n"/>
+      <c r="Z12" s="153" t="n"/>
+      <c r="AA12" s="153" t="n"/>
+      <c r="AB12" s="153" t="n"/>
+      <c r="AC12" s="153" t="n"/>
+      <c r="AD12" s="153" t="n"/>
+      <c r="AE12" s="153" t="n"/>
+      <c r="AF12" s="153" t="n"/>
+      <c r="AG12" s="153" t="n"/>
+      <c r="AH12" s="153" t="n"/>
+      <c r="AI12" s="153" t="n"/>
+      <c r="AJ12" s="153" t="n"/>
+      <c r="AK12" s="153" t="n"/>
+      <c r="AL12" s="153" t="n"/>
+      <c r="AM12" s="153" t="n"/>
+      <c r="AN12" s="155" t="n"/>
       <c r="AO12" s="148" t="inlineStr">
         <is>
           <t>E</t>
@@ -15551,7 +15255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col width="8.625" customWidth="1" style="1" min="1" max="1"/>
@@ -15642,11 +15346,7 @@
     </row>
     <row r="15" ht="28.15" customHeight="1" s="294">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        线材                          端子</t>
-        </is>
-      </c>
+      <c r="B15" s="12" t="n"/>
       <c r="C15" s="6" t="n"/>
     </row>
     <row r="16" ht="28.15" customHeight="1" s="294">
